--- a/Input_data_DE_handson_SQL_handson.xlsx
+++ b/Input_data_DE_handson_SQL_handson.xlsx
@@ -5,19 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\All_Notes_from_learning\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\All_Notes_from_learning\All_Notes_to_Share\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5CA35B-A88D-4F55-B94F-BB098A6DFE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A004B81F-8FC9-4FB4-9003-EC565C9C8100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23310" windowHeight="13740" activeTab="1" xr2:uid="{206FDF6F-FA47-4BC2-86A3-889E3E646FC4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Cust_Tables" sheetId="1" r:id="rId1"/>
+    <sheet name="Sales_Tables" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="85">
   <si>
     <t>Employee</t>
   </si>
@@ -74,9 +73,6 @@
     <t>login_Date</t>
   </si>
   <si>
-    <t xml:space="preserve">DDL missing </t>
-  </si>
-  <si>
     <t>Sales</t>
   </si>
   <si>
@@ -147,13 +143,160 @@
   </si>
   <si>
     <t>prod_id</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>Projects</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>emp01</t>
+  </si>
+  <si>
+    <t>emp02</t>
+  </si>
+  <si>
+    <t>emp03</t>
+  </si>
+  <si>
+    <t>emp04</t>
+  </si>
+  <si>
+    <t>emp05</t>
+  </si>
+  <si>
+    <t>emp06</t>
+  </si>
+  <si>
+    <t>emp07</t>
+  </si>
+  <si>
+    <t>emp08</t>
+  </si>
+  <si>
+    <t>emp09</t>
+  </si>
+  <si>
+    <t>emp10</t>
+  </si>
+  <si>
+    <t>emp11</t>
+  </si>
+  <si>
+    <t>emp12</t>
+  </si>
+  <si>
+    <t>emp13</t>
+  </si>
+  <si>
+    <t>emp14</t>
+  </si>
+  <si>
+    <t>emp15</t>
+  </si>
+  <si>
+    <t>emp16</t>
+  </si>
+  <si>
+    <t>emp17</t>
+  </si>
+  <si>
+    <t>emp18</t>
+  </si>
+  <si>
+    <t>emp19</t>
+  </si>
+  <si>
+    <t>emp20</t>
+  </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>CXO</t>
+  </si>
+  <si>
+    <t>Adminstaff</t>
+  </si>
+  <si>
+    <t>HR recruitment</t>
+  </si>
+  <si>
+    <t>HR Payroll</t>
+  </si>
+  <si>
+    <t>Digital marketing</t>
+  </si>
+  <si>
+    <t>Media rep</t>
+  </si>
+  <si>
+    <t>Publishing</t>
+  </si>
+  <si>
+    <t>Dev1</t>
+  </si>
+  <si>
+    <t>Dev2</t>
+  </si>
+  <si>
+    <t>Dev3</t>
+  </si>
+  <si>
+    <t>Tester1</t>
+  </si>
+  <si>
+    <t>Tester2</t>
+  </si>
+  <si>
+    <t>Proj_1_lead</t>
+  </si>
+  <si>
+    <t>Proj_2_lead</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>SM_Admin</t>
+  </si>
+  <si>
+    <t>SM_HR</t>
+  </si>
+  <si>
+    <t>SM_Media</t>
+  </si>
+  <si>
+    <t>SM_Projects</t>
+  </si>
+  <si>
+    <t>SM_Sales</t>
+  </si>
+  <si>
+    <t>Sale1</t>
+  </si>
+  <si>
+    <t>Sale2</t>
+  </si>
+  <si>
+    <t>Sale3</t>
+  </si>
+  <si>
+    <t>Sale4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,16 +304,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -178,12 +347,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,91 +687,750 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEFAA317-687F-48AA-BF11-BD28920B8B88}">
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="4" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="Q1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>10</v>
+      </c>
+      <c r="R2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B4" s="5">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B5" s="5">
+        <v>11</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="5">
+        <v>100</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B6" s="5">
+        <v>22</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="5">
+        <v>200</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B7" s="5">
+        <v>33</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="5">
+        <v>300</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="5">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B8" s="5">
+        <v>44</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="5">
+        <v>400</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B9" s="5">
+        <v>55</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="5">
+        <v>500</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B10" s="5">
+        <v>110</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="5">
+        <v>100</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="5">
+        <v>11</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B11" s="5">
+        <v>210</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="5">
+        <v>200</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="5">
+        <v>22</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
+        <v>211</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="5">
+        <v>200</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="5">
+        <v>22</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="5">
+        <v>310</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="5">
+        <v>300</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="5">
+        <v>33</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
+        <v>311</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="5">
+        <v>300</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="5">
+        <v>33</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B15" s="5">
+        <v>312</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="5">
+        <v>300</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="5">
+        <v>33</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
+        <v>410</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="5">
+        <v>400</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="5">
+        <v>44</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
+        <v>411</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="5">
+        <v>400</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="5">
+        <v>44</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
+        <v>412</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="5">
+        <v>400</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="5">
+        <v>44</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="5">
+        <v>413</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="5">
+        <v>400</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="5">
+        <v>44</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="5">
+        <v>510</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="5">
+        <v>500</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="5">
+        <v>55</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="5">
+        <v>511</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="5">
+        <v>500</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" s="5">
+        <v>55</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="5">
+        <v>520</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="5">
+        <v>500</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="5">
+        <v>510</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="5">
+        <v>521</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="5">
+        <v>500</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="5">
+        <v>511</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="5">
+        <v>522</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="5">
+        <v>500</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="5">
+        <v>511</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="5">
+        <v>523</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5">
+        <v>500</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="5">
+        <v>510</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="5">
+        <v>524</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5">
+        <v>500</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="5">
+        <v>511</v>
+      </c>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="P1" t="s">
-        <v>9</v>
-      </c>
-      <c r="S1" t="s">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="5">
+        <v>1</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="5">
+        <v>100</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="5">
+        <v>200</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="5">
+        <v>300</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="5">
+        <v>400</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="5">
+        <v>500</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="5">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="5">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="s">
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="5">
         <v>11</v>
       </c>
-      <c r="S2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>13</v>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="5">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="5">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="5">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="5">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="5">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="5">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="5">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="5">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="5">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="5">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="5">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="5">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="5">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="5">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="5">
+        <v>524</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -599,69 +1447,69 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2" t="s">
         <v>34</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" t="s">
-        <v>34</v>
-      </c>
-      <c r="U2" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Input_data_DE_handson_SQL_handson.xlsx
+++ b/Input_data_DE_handson_SQL_handson.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\All_Notes_from_learning\All_Notes_to_Share\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A004B81F-8FC9-4FB4-9003-EC565C9C8100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EF2470-110A-42C2-BB49-4189A4987CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23310" windowHeight="13740" activeTab="1" xr2:uid="{206FDF6F-FA47-4BC2-86A3-889E3E646FC4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23310" windowHeight="13740" xr2:uid="{206FDF6F-FA47-4BC2-86A3-889E3E646FC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Cust_Tables" sheetId="1" r:id="rId1"/>
@@ -366,13 +366,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,6 +696,7 @@
     <col min="3" max="3" width="11.42578125" customWidth="1"/>
     <col min="4" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -757,7 +759,9 @@
         <v>60</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="G3" s="6">
+        <v>37987</v>
+      </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
@@ -777,7 +781,9 @@
       <c r="F4" s="5">
         <v>1</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="6">
+        <v>38353</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
@@ -797,7 +803,9 @@
       <c r="F5" s="5">
         <v>2</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="6">
+        <v>39083</v>
+      </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
     </row>
@@ -817,7 +825,9 @@
       <c r="F6" s="5">
         <v>2</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="6">
+        <v>38718</v>
+      </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
@@ -837,7 +847,9 @@
       <c r="F7" s="5">
         <v>2</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="6">
+        <v>39448</v>
+      </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
     </row>
@@ -857,7 +869,9 @@
       <c r="F8" s="5">
         <v>2</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="6">
+        <v>38353</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
@@ -877,7 +891,9 @@
       <c r="F9" s="5">
         <v>2</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="6">
+        <v>38353</v>
+      </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
     </row>
@@ -897,7 +913,9 @@
       <c r="F10" s="5">
         <v>11</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="6">
+        <v>40179</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
@@ -917,7 +935,9 @@
       <c r="F11" s="5">
         <v>22</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="6">
+        <v>40179</v>
+      </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
     </row>
@@ -937,7 +957,9 @@
       <c r="F12" s="5">
         <v>22</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12" s="6">
+        <v>43831</v>
+      </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
@@ -957,7 +979,9 @@
       <c r="F13" s="5">
         <v>33</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="6">
+        <v>40179</v>
+      </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
     </row>
@@ -977,7 +1001,9 @@
       <c r="F14" s="5">
         <v>33</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="6">
+        <v>42005</v>
+      </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
@@ -997,7 +1023,9 @@
       <c r="F15" s="5">
         <v>33</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="6">
+        <v>43831</v>
+      </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
@@ -1017,7 +1045,9 @@
       <c r="F16" s="5">
         <v>44</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="G16" s="6">
+        <v>40179</v>
+      </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
@@ -1037,7 +1067,9 @@
       <c r="F17" s="5">
         <v>44</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="G17" s="6">
+        <v>42005</v>
+      </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
     </row>
@@ -1057,7 +1089,9 @@
       <c r="F18" s="5">
         <v>44</v>
       </c>
-      <c r="G18" s="5"/>
+      <c r="G18" s="6">
+        <v>43831</v>
+      </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
@@ -1077,7 +1111,9 @@
       <c r="F19" s="5">
         <v>44</v>
       </c>
-      <c r="G19" s="5"/>
+      <c r="G19" s="6">
+        <v>44197</v>
+      </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
     </row>
@@ -1097,7 +1133,9 @@
       <c r="F20" s="5">
         <v>55</v>
       </c>
-      <c r="G20" s="5"/>
+      <c r="G20" s="6">
+        <v>38353</v>
+      </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
@@ -1117,7 +1155,9 @@
       <c r="F21" s="5">
         <v>55</v>
       </c>
-      <c r="G21" s="5"/>
+      <c r="G21" s="6">
+        <v>39083</v>
+      </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
     </row>
@@ -1137,7 +1177,9 @@
       <c r="F22" s="5">
         <v>510</v>
       </c>
-      <c r="G22" s="5"/>
+      <c r="G22" s="6">
+        <v>40179</v>
+      </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
@@ -1157,7 +1199,9 @@
       <c r="F23" s="5">
         <v>511</v>
       </c>
-      <c r="G23" s="5"/>
+      <c r="G23" s="6">
+        <v>40179</v>
+      </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
     </row>
@@ -1177,7 +1221,9 @@
       <c r="F24" s="5">
         <v>511</v>
       </c>
-      <c r="G24" s="5"/>
+      <c r="G24" s="6">
+        <v>42005</v>
+      </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
@@ -1195,7 +1241,9 @@
       <c r="F25" s="5">
         <v>510</v>
       </c>
-      <c r="G25" s="5"/>
+      <c r="G25" s="6">
+        <v>42736</v>
+      </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
     </row>
@@ -1213,7 +1261,9 @@
       <c r="F26" s="5">
         <v>511</v>
       </c>
-      <c r="G26" s="5"/>
+      <c r="G26" s="6">
+        <v>44197</v>
+      </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>

--- a/Input_data_DE_handson_SQL_handson.xlsx
+++ b/Input_data_DE_handson_SQL_handson.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\All_Notes_from_learning\All_Notes_to_Share\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EF2470-110A-42C2-BB49-4189A4987CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E4C67F-F590-42CF-8C86-0B9463AC1B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23310" windowHeight="13740" xr2:uid="{206FDF6F-FA47-4BC2-86A3-889E3E646FC4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23310" windowHeight="13740" activeTab="1" xr2:uid="{206FDF6F-FA47-4BC2-86A3-889E3E646FC4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cust_Tables" sheetId="1" r:id="rId1"/>
-    <sheet name="Sales_Tables" sheetId="2" r:id="rId2"/>
+    <sheet name="DDL" sheetId="3" r:id="rId1"/>
+    <sheet name="Cust_Tables" sheetId="1" r:id="rId2"/>
+    <sheet name="Sales_Tables" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="85">
-  <si>
-    <t>Employee</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="96">
   <si>
     <t>emp_id</t>
   </si>
@@ -157,12 +155,6 @@
     <t>Media</t>
   </si>
   <si>
-    <t>emp01</t>
-  </si>
-  <si>
-    <t>emp02</t>
-  </si>
-  <si>
     <t>emp03</t>
   </si>
   <si>
@@ -193,12 +185,6 @@
     <t>emp12</t>
   </si>
   <si>
-    <t>emp13</t>
-  </si>
-  <si>
-    <t>emp14</t>
-  </si>
-  <si>
     <t>emp15</t>
   </si>
   <si>
@@ -208,9 +194,6 @@
     <t>emp17</t>
   </si>
   <si>
-    <t>emp18</t>
-  </si>
-  <si>
     <t>emp19</t>
   </si>
   <si>
@@ -241,21 +224,6 @@
     <t>Publishing</t>
   </si>
   <si>
-    <t>Dev1</t>
-  </si>
-  <si>
-    <t>Dev2</t>
-  </si>
-  <si>
-    <t>Dev3</t>
-  </si>
-  <si>
-    <t>Tester1</t>
-  </si>
-  <si>
-    <t>Tester2</t>
-  </si>
-  <si>
     <t>Proj_1_lead</t>
   </si>
   <si>
@@ -290,12 +258,81 @@
   </si>
   <si>
     <t>Sale4</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Insert Statements</t>
+  </si>
+  <si>
+    <t>Employees</t>
+  </si>
+  <si>
+    <t>CREATE TABLE employees (emp_id INT PRIMARY KEY, emp_name VARCHAR(100) NOT NULL, dept_id INT, job_title VARCHAR(100), manager_id INT, join_date DATE, salary DECIMAL(12,2), gender CHAR(1));</t>
+  </si>
+  <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>interview</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>employees</t>
+  </si>
+  <si>
+    <t>DDL</t>
+  </si>
+  <si>
+    <t>create database interview;</t>
+  </si>
+  <si>
+    <t>emp21</t>
+  </si>
+  <si>
+    <t>emp22</t>
+  </si>
+  <si>
+    <t>Ramesh</t>
+  </si>
+  <si>
+    <t>Suresh</t>
+  </si>
+  <si>
+    <t>Future</t>
+  </si>
+  <si>
+    <t>Dev</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>emp23</t>
+  </si>
+  <si>
+    <t>emp24</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>NULL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-14009]yyyy/mm/dd;@"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -319,7 +356,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,6 +372,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -366,14 +433,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -687,21 +763,67 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA423CCC-EAB1-416C-A476-0F192CAEA664}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="133.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEFAA317-687F-48AA-BF11-BD28920B8B88}">
-  <dimension ref="A1:R62"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" customWidth="1"/>
     <col min="4" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -709,774 +831,1461 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="Q1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>5</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>10</v>
-      </c>
-      <c r="R2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" s="5">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D3" s="5">
         <v>1</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="G3" s="6">
+      <c r="G3" s="7">
         <v>37987</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H3" s="14">
+        <v>5000000</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" t="str">
+        <f>"INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES ("&amp;B3&amp;", '"&amp;C3&amp;"', "&amp;IF(D3="","NULL",D3)&amp;", '"&amp;E3&amp;"', "&amp;IF(F3="","NULL",F3)&amp;", '"&amp;TEXT(G3,"yyyy-mm-dd")&amp;"', "&amp;H3&amp;", '"&amp;IF(I3="","NULL",I3)&amp;"');"</f>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (1, 'CEO', 1, 'CEO', NULL, '2004-01-01', 5000000, 'M');</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" s="5">
         <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D4" s="5">
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F4" s="5">
         <v>1</v>
       </c>
-      <c r="G4" s="6">
-        <v>38353</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G4" s="7">
+        <v>41640</v>
+      </c>
+      <c r="H4" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" t="str">
+        <f t="shared" ref="K4:K28" si="0">"INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES ("&amp;B4&amp;", '"&amp;C4&amp;"', "&amp;IF(D4="","NULL",D4)&amp;", '"&amp;E4&amp;"', "&amp;IF(F4="","NULL",F4)&amp;", '"&amp;TEXT(G4,"yyyy-mm-dd")&amp;"', "&amp;H4&amp;", '"&amp;IF(I4="","NULL",I4)&amp;"');"</f>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (2, 'CXO', 1, 'CXO', 1, '2014-01-01', 3000000, 'F');</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>11</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>40</v>
+      <c r="C5" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="D5" s="5">
         <v>100</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F5" s="5">
         <v>2</v>
       </c>
-      <c r="G5" s="6">
-        <v>39083</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G5" s="7">
+        <v>42370</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2000000</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (11, 'Ramesh', 100, 'SM_Admin', 2, '2016-01-01', 2000000, 'M');</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>22</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>41</v>
+      <c r="C6" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="D6" s="5">
         <v>200</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="F6" s="5">
         <v>2</v>
       </c>
-      <c r="G6" s="6">
-        <v>38718</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G6" s="7">
+        <v>42005</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2100000</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (22, 'Suresh', 200, 'SM_HR', 2, '2015-01-01', 2100000, 'M');</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>33</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D7" s="5">
         <v>300</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F7" s="5">
         <v>2</v>
       </c>
-      <c r="G7" s="6">
-        <v>39448</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G7" s="7">
+        <v>41640</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2200000</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (33, 'emp03', 300, 'SM_Media', 2, '2014-01-01', 2200000, 'F');</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>44</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D8" s="5">
         <v>400</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F8" s="5">
         <v>2</v>
       </c>
-      <c r="G8" s="6">
-        <v>38353</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="5">
+      <c r="G8" s="7">
+        <v>37987</v>
+      </c>
+      <c r="H8" s="13">
+        <v>2300000</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (44, 'emp04', 400, 'SM_Sales', 2, '2004-01-01', 2300000, 'M');</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B9" s="8">
         <v>55</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D9" s="5">
         <v>500</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="F9" s="5">
         <v>2</v>
       </c>
-      <c r="G9" s="6">
-        <v>38353</v>
-      </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G9" s="7">
+        <v>38018</v>
+      </c>
+      <c r="H9" s="8">
+        <v>2500000</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (55, 'emp05', 500, 'SM_Projects', 2, '2004-02-01', 2500000, 'M');</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>110</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" s="5">
         <v>100</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F10" s="5">
         <v>11</v>
       </c>
-      <c r="G10" s="6">
-        <v>40179</v>
-      </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G10" s="7">
+        <v>44562</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1500000</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (110, 'emp06', 100, 'Adminstaff', 11, '2022-01-01', 1500000, 'M');</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>210</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D11" s="5">
         <v>200</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F11" s="5">
         <v>22</v>
       </c>
-      <c r="G11" s="6">
-        <v>40179</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G11" s="7">
+        <v>42370</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1700000</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (210, 'emp07', 200, 'HR recruitment', 22, '2016-01-01', 1700000, 'F');</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>211</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D12" s="5">
         <v>200</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F12" s="5">
         <v>22</v>
       </c>
-      <c r="G12" s="6">
-        <v>43831</v>
-      </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G12" s="7">
+        <v>44562</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1600000</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (211, 'emp08', 200, 'HR Payroll', 22, '2022-01-01', 1600000, 'M');</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>310</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="5">
         <v>300</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F13" s="5">
         <v>33</v>
       </c>
-      <c r="G13" s="6">
-        <v>40179</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G13" s="7">
+        <v>40909</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1750000</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (310, 'emp09', 300, 'Digital marketing', 33, '2012-01-01', 1750000, 'F');</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>311</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D14" s="5">
         <v>300</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F14" s="5">
         <v>33</v>
       </c>
-      <c r="G14" s="6">
-        <v>42005</v>
-      </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G14" s="7">
+        <v>43831</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1650000</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (311, 'emp10', 300, 'Media rep', 33, '2020-01-01', 1650000, 'M');</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>312</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D15" s="5">
         <v>300</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F15" s="5">
         <v>33</v>
       </c>
-      <c r="G15" s="6">
-        <v>43831</v>
-      </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G15" s="7">
+        <v>45292</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1550000</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K15" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (312, 'emp11', 300, 'Publishing', 33, '2024-01-01', 1550000, 'M');</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>410</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D16" s="5">
         <v>400</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F16" s="5">
         <v>44</v>
       </c>
-      <c r="G16" s="6">
-        <v>40179</v>
-      </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G16" s="7">
+        <v>38718</v>
+      </c>
+      <c r="H16" s="13">
+        <v>2300000</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (410, 'emp12', 400, 'Sale1', 44, '2006-01-01', 2300000, 'M');</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
         <v>411</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>52</v>
+      <c r="C17" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="D17" s="5">
         <v>400</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F17" s="5">
         <v>44</v>
       </c>
-      <c r="G17" s="6">
-        <v>42005</v>
-      </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G17" s="7">
+        <v>41275</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1780000</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (411, 'Ramesh', 400, 'Sale2', 44, '2013-01-01', 1780000, 'M');</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B18" s="5">
         <v>412</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>53</v>
+      <c r="C18" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="D18" s="5">
         <v>400</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F18" s="5">
         <v>44</v>
       </c>
-      <c r="G18" s="6">
-        <v>43831</v>
-      </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G18" s="7">
+        <v>44562</v>
+      </c>
+      <c r="H18" s="5">
+        <v>1680000</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (412, 'Suresh', 400, 'Sale3', 44, '2022-01-01', 1680000, 'M');</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" s="5">
         <v>413</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D19" s="5">
         <v>400</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F19" s="5">
         <v>44</v>
       </c>
-      <c r="G19" s="6">
-        <v>44197</v>
-      </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G19" s="7">
+        <v>45292</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1580000</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (413, 'emp15', 400, 'Sale4', 44, '2024-01-01', 1580000, 'F');</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" s="5">
         <v>510</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D20" s="5">
         <v>500</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F20" s="5">
         <v>55</v>
       </c>
-      <c r="G20" s="6">
-        <v>38353</v>
-      </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="5">
+      <c r="G20" s="7">
+        <v>37987</v>
+      </c>
+      <c r="H20" s="5">
+        <v>2000000</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (510, 'emp16', 500, 'Proj_1_lead', 55, '2004-01-01', 2000000, 'M');</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="8">
         <v>511</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D21" s="5">
         <v>500</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="5">
+        <v>63</v>
+      </c>
+      <c r="F21" s="8">
         <v>55</v>
       </c>
-      <c r="G21" s="6">
-        <v>39083</v>
-      </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G21" s="7">
+        <v>38718</v>
+      </c>
+      <c r="H21" s="8">
+        <v>2700000</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (511, 'emp17', 500, 'Proj_2_lead', 55, '2006-01-01', 2700000, 'F');</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B22" s="5">
         <v>520</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>57</v>
+      <c r="C22" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="D22" s="5">
         <v>500</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F22" s="5">
         <v>510</v>
       </c>
-      <c r="G22" s="6">
-        <v>40179</v>
-      </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G22" s="7">
+        <v>42370</v>
+      </c>
+      <c r="H22" s="5">
+        <v>2150000</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K22" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (520, 'Ramesh', 500, 'Dev', 510, '2016-01-01', 2150000, 'M');</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B23" s="5">
         <v>521</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D23" s="5">
         <v>500</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="5">
+        <v>90</v>
+      </c>
+      <c r="F23" s="8">
         <v>511</v>
       </c>
-      <c r="G23" s="6">
-        <v>40179</v>
-      </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G23" s="7">
+        <v>42736</v>
+      </c>
+      <c r="H23" s="8">
+        <v>2750000</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K23" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (521, 'emp19', 500, 'Dev', 511, '2017-01-01', 2750000, 'F');</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B24" s="5">
         <v>522</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D24" s="5">
         <v>500</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F24" s="5">
         <v>511</v>
       </c>
-      <c r="G24" s="6">
-        <v>42005</v>
-      </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G24" s="7">
+        <v>43101</v>
+      </c>
+      <c r="H24" s="5">
+        <v>1000000</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K24" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (522, 'emp20', 500, 'Dev', 511, '2018-01-01', 1000000, 'M');</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B25" s="5">
         <v>523</v>
       </c>
-      <c r="C25" s="5"/>
+      <c r="C25" s="5" t="s">
+        <v>85</v>
+      </c>
       <c r="D25" s="5">
         <v>500</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="F25" s="5">
         <v>510</v>
       </c>
-      <c r="G25" s="6">
-        <v>42736</v>
-      </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G25" s="7">
+        <v>42370</v>
+      </c>
+      <c r="H25" s="5">
+        <v>1100000</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K25" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (523, 'emp21', 500, 'Tester', 510, '2016-01-01', 1100000, 'M');</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B26" s="5">
         <v>524</v>
       </c>
-      <c r="C26" s="5"/>
+      <c r="C26" s="5" t="s">
+        <v>86</v>
+      </c>
       <c r="D26" s="5">
         <v>500</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F26" s="5">
         <v>511</v>
       </c>
-      <c r="G26" s="6">
-        <v>44197</v>
-      </c>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="G26" s="7">
+        <v>45658</v>
+      </c>
+      <c r="H26" s="5">
+        <v>1200000</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K26" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (524, 'emp22', 500, 'Tester', 511, '2025-01-01', 1200000, 'F');</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="5">
+        <v>1001</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="5">
+        <v>11</v>
+      </c>
+      <c r="G27" s="7">
+        <v>45658</v>
+      </c>
+      <c r="H27" s="5">
+        <v>120000</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K27" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (1001, 'emp23', NULL, 'Housekeeping', 11, '2025-01-01', 120000, 'M');</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="5">
+        <v>1002</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="5">
+        <v>11</v>
+      </c>
+      <c r="G28" s="7">
+        <v>45658</v>
+      </c>
+      <c r="H28" s="5">
+        <v>110000</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K28" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO employees (emp_id, emp_name, dept_id, job_title, manager_id, join_date, salary, gender) VALUES (1002, 'emp24', NULL, 'Housekeeping', 11, '2025-01-01', 110000, 'F');</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="5">
+      <c r="K31" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B32" s="5">
         <v>1</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="5">
+      <c r="C32" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K32" t="str">
+        <f>"INSERT INTO departments (dept_id, dept_name) VALUES ("&amp;B32&amp;", '"&amp;C32&amp;"');"</f>
+        <v>INSERT INTO departments (dept_id, dept_name) VALUES (1, 'Management');</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="5">
         <v>100</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K33" t="str">
+        <f t="shared" ref="K33:K38" si="1">"INSERT INTO departments (dept_id, dept_name) VALUES ("&amp;B33&amp;", '"&amp;C33&amp;"');"</f>
+        <v>INSERT INTO departments (dept_id, dept_name) VALUES (100, 'Administration');</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B34" s="5">
+        <v>200</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K34" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO departments (dept_id, dept_name) VALUES (200, 'HR');</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="5">
+        <v>300</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K35" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO departments (dept_id, dept_name) VALUES (300, 'Media');</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B36" s="5">
+        <v>400</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K36" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO departments (dept_id, dept_name) VALUES (400, 'Sales');</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B37" s="5">
+        <v>500</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="5">
-        <v>200</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="5">
-        <v>300</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="5">
-        <v>400</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="5">
-        <v>500</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="K37" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO departments (dept_id, dept_name) VALUES (500, 'Projects');</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B38" s="12">
+        <v>999</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="K38" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO departments (dept_id, dept_name) VALUES (999, 'Future');</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="3" t="s">
+      <c r="D41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="5">
         <v>1</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="5">
+      <c r="C42" s="7">
+        <v>37987</v>
+      </c>
+      <c r="D42" t="s">
+        <v>95</v>
+      </c>
+      <c r="E42" s="5">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B43" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B40" s="5">
+      <c r="C43" s="7">
+        <v>39814</v>
+      </c>
+      <c r="D43" s="5">
+        <v>2000000</v>
+      </c>
+      <c r="E43" s="5">
+        <v>2300000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="5">
+        <v>1</v>
+      </c>
+      <c r="C44" s="7">
+        <v>41640</v>
+      </c>
+      <c r="D44" s="5">
+        <v>2300000</v>
+      </c>
+      <c r="E44" s="5">
+        <v>3200000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B45" s="5">
+        <v>1</v>
+      </c>
+      <c r="C45" s="7">
+        <v>45292</v>
+      </c>
+      <c r="D45" s="5">
+        <v>3200000</v>
+      </c>
+      <c r="E45" s="5">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="5">
+      <c r="C46" s="7">
+        <v>41640</v>
+      </c>
+      <c r="D46" t="s">
+        <v>95</v>
+      </c>
+      <c r="E46" s="5">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B47" s="5">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>43831</v>
+      </c>
+      <c r="D47" s="5">
+        <v>1500000</v>
+      </c>
+      <c r="E47" s="5">
+        <v>2200000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="5">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>45658</v>
+      </c>
+      <c r="D48" s="5">
+        <v>2200000</v>
+      </c>
+      <c r="E48" s="5">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="5">
         <v>11</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="5">
+      <c r="C49" s="7">
+        <v>42370</v>
+      </c>
+      <c r="D49" t="s">
+        <v>95</v>
+      </c>
+      <c r="E49" s="5">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="5">
+        <v>11</v>
+      </c>
+      <c r="C50" s="7">
+        <v>42370</v>
+      </c>
+      <c r="D50" s="5">
+        <v>1500000</v>
+      </c>
+      <c r="E50" s="5">
+        <v>1750000</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="5">
+        <v>11</v>
+      </c>
+      <c r="C51" s="7">
+        <v>42370</v>
+      </c>
+      <c r="D51" s="5">
+        <v>1750000</v>
+      </c>
+      <c r="E51" s="5">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" s="5">
         <v>22</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="5">
+      <c r="C52" s="7">
+        <v>42005</v>
+      </c>
+      <c r="D52" t="s">
+        <v>95</v>
+      </c>
+      <c r="E52" s="5">
+        <v>1600000</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" s="5">
+        <v>22</v>
+      </c>
+      <c r="C53" s="7">
+        <v>43466</v>
+      </c>
+      <c r="D53" s="5">
+        <v>1600000</v>
+      </c>
+      <c r="E53" s="5">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="5">
+        <v>22</v>
+      </c>
+      <c r="C54" s="7">
+        <v>45658</v>
+      </c>
+      <c r="D54" s="5">
+        <v>1800000</v>
+      </c>
+      <c r="E54" s="5">
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="5">
         <v>33</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="5">
+      <c r="C55" s="7">
+        <v>41640</v>
+      </c>
+      <c r="D55" t="s">
+        <v>95</v>
+      </c>
+      <c r="E55" s="5">
+        <v>2200000</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56" s="5">
         <v>44</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="5">
+      <c r="C56" s="7">
+        <v>37987</v>
+      </c>
+      <c r="D56" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="5">
+        <v>2300000</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" s="5">
         <v>55</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="5">
+      <c r="C57" s="7">
+        <v>38018</v>
+      </c>
+      <c r="D57" t="s">
+        <v>95</v>
+      </c>
+      <c r="E57" s="5">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" s="5">
         <v>110</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="5">
+      <c r="C58" s="7">
+        <v>44562</v>
+      </c>
+      <c r="D58" t="s">
+        <v>95</v>
+      </c>
+      <c r="E58" s="5">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="5">
+      <c r="C59" s="7">
+        <v>42370</v>
+      </c>
+      <c r="D59" t="s">
+        <v>95</v>
+      </c>
+      <c r="E59" s="5">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="5">
         <v>211</v>
       </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="5">
+      <c r="C60" s="7">
+        <v>44562</v>
+      </c>
+      <c r="D60" t="s">
+        <v>95</v>
+      </c>
+      <c r="E60" s="5">
+        <v>1600000</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" s="5">
         <v>310</v>
       </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="5">
+      <c r="C61" s="7">
+        <v>40909</v>
+      </c>
+      <c r="D61" t="s">
+        <v>95</v>
+      </c>
+      <c r="E61" s="5">
+        <v>1750000</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="5">
         <v>311</v>
       </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="5">
+      <c r="C62" s="7">
+        <v>43831</v>
+      </c>
+      <c r="D62" t="s">
+        <v>95</v>
+      </c>
+      <c r="E62" s="5">
+        <v>1650000</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" s="5">
         <v>312</v>
       </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" s="5">
+      <c r="C63" s="7">
+        <v>45292</v>
+      </c>
+      <c r="D63" t="s">
+        <v>95</v>
+      </c>
+      <c r="E63" s="5">
+        <v>1550000</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" s="5">
         <v>410</v>
       </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" s="5">
+      <c r="C64" s="7">
+        <v>38718</v>
+      </c>
+      <c r="D64" t="s">
+        <v>95</v>
+      </c>
+      <c r="E64" s="5">
+        <v>2300000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B65" s="5">
         <v>411</v>
       </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" s="5">
+      <c r="C65" s="7">
+        <v>41275</v>
+      </c>
+      <c r="D65" t="s">
+        <v>95</v>
+      </c>
+      <c r="E65" s="5">
+        <v>1780000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B66" s="5">
         <v>412</v>
       </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" s="5">
+      <c r="C66" s="7">
+        <v>44562</v>
+      </c>
+      <c r="D66" t="s">
+        <v>95</v>
+      </c>
+      <c r="E66" s="5">
+        <v>1680000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B67" s="5">
         <v>413</v>
       </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56" s="5">
+      <c r="C67" s="7">
+        <v>45292</v>
+      </c>
+      <c r="D67" t="s">
+        <v>95</v>
+      </c>
+      <c r="E67" s="5">
+        <v>1580000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B68" s="5">
         <v>510</v>
       </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57" s="5">
+      <c r="C68" s="7">
+        <v>37987</v>
+      </c>
+      <c r="D68" t="s">
+        <v>95</v>
+      </c>
+      <c r="E68" s="5">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B69" s="5">
         <v>511</v>
       </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B58" s="5">
+      <c r="C69" s="7">
+        <v>38718</v>
+      </c>
+      <c r="D69" t="s">
+        <v>95</v>
+      </c>
+      <c r="E69" s="5">
+        <v>2700000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B70" s="5">
         <v>520</v>
       </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59" s="5">
+      <c r="C70" s="7">
+        <v>42370</v>
+      </c>
+      <c r="D70" t="s">
+        <v>95</v>
+      </c>
+      <c r="E70" s="5">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B71" s="5">
         <v>521</v>
       </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" s="5">
+      <c r="C71" s="7">
+        <v>42736</v>
+      </c>
+      <c r="D71" t="s">
+        <v>95</v>
+      </c>
+      <c r="E71" s="5">
+        <v>2750000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B72" s="5">
         <v>522</v>
       </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B61" s="5">
+      <c r="C72" s="7">
+        <v>43101</v>
+      </c>
+      <c r="D72" t="s">
+        <v>95</v>
+      </c>
+      <c r="E72" s="5">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B73" s="5">
         <v>523</v>
       </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B62" s="5">
+      <c r="C73" s="7">
+        <v>42370</v>
+      </c>
+      <c r="D73" t="s">
+        <v>95</v>
+      </c>
+      <c r="E73" s="5">
+        <v>1100000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B74" s="5">
         <v>524</v>
+      </c>
+      <c r="C74" s="7">
+        <v>45658</v>
+      </c>
+      <c r="D74" t="s">
+        <v>95</v>
+      </c>
+      <c r="E74" s="5">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B75" s="5">
+        <v>1001</v>
+      </c>
+      <c r="C75" s="7">
+        <v>45658</v>
+      </c>
+      <c r="D75" t="s">
+        <v>95</v>
+      </c>
+      <c r="E75" s="5">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B76" s="5">
+        <v>1002</v>
+      </c>
+      <c r="C76" s="7">
+        <v>45658</v>
+      </c>
+      <c r="D76" t="s">
+        <v>95</v>
+      </c>
+      <c r="E76" s="5">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B77" s="11"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B78" s="11"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1485,7 +2294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D58C449-1D1C-42CF-89F2-FA996C663289}">
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1497,69 +2306,69 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" t="s">
         <v>33</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U2" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
